--- a/output/tables/APPENDIX_species_summary.xlsx
+++ b/output/tables/APPENDIX_species_summary.xlsx
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>

--- a/output/tables/APPENDIX_species_summary.xlsx
+++ b/output/tables/APPENDIX_species_summary.xlsx
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
